--- a/reports/hazop_system_13.xlsx
+++ b/reports/hazop_system_13.xlsx
@@ -57,7 +57,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -67,6 +67,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -87,7 +92,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -97,6 +102,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -538,10 +546,10 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -1034,116 +1042,116 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>No flow</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>blocked line / closed valve (generic); pump/compressor stop (generic)</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>loss of process function (generic); functions affected: 13-XV2271; safety functions in node: 13-XV2271, 13-ZL2271, 13-ZS2271</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>13-XV2271</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr"/>
-      <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr"/>
+      <c r="F4" s="7" t="inlineStr"/>
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Low flow</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>partial blockage / fouling (generic)</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>reduced capacity (generic); functions affected: 13-XV2271; safety functions in node: 13-XV2271, 13-ZL2271, 13-ZS2271</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>13-XV2271</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>High flow</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>control valve fully open (generic)</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>possible downstream overload (generic); functions affected: 13-XV2271; safety functions in node: 13-XV2271, 13-ZL2271, 13-ZS2271</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>13-XV2271</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr"/>
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Reverse flow</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>check-valve failure / pressure reversal (generic)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>possible contamination / backflow to upstream (generic); functions affected: 13-XV2271; safety functions in node: 13-XV2271, 13-ZL2271, 13-ZS2271</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>13-XV2271</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1224,116 +1232,116 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>No flow</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>blocked line / closed valve (generic); pump/compressor stop (generic)</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>loss of process function (generic); functions affected: 13-XV2272; safety functions in node: 13-XV2272, 13-ZL2272, 13-ZS2272</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>13-XV2272</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr"/>
-      <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr"/>
+      <c r="F4" s="7" t="inlineStr"/>
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Low flow</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>partial blockage / fouling (generic)</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>reduced capacity (generic); functions affected: 13-XV2272; safety functions in node: 13-XV2272, 13-ZL2272, 13-ZS2272</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>13-XV2272</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>High flow</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>control valve fully open (generic)</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>possible downstream overload (generic); functions affected: 13-XV2272; safety functions in node: 13-XV2272, 13-ZL2272, 13-ZS2272</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>13-XV2272</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr"/>
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Reverse flow</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>check-valve failure / pressure reversal (generic)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>possible contamination / backflow to upstream (generic); functions affected: 13-XV2272; safety functions in node: 13-XV2272, 13-ZL2272, 13-ZS2272</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>13-XV2272</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1414,116 +1422,116 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>No flow</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>blocked line / closed valve (generic); pump/compressor stop (generic)</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>loss of process function (generic)</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>(none found in extraction — verify)</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr"/>
-      <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr"/>
+      <c r="F4" s="7" t="inlineStr"/>
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Low flow</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>partial blockage / fouling (generic)</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>reduced capacity (generic)</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>(none found in extraction — verify)</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>High flow</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>control valve fully open (generic)</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>possible downstream overload (generic)</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>(none found in extraction — verify)</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr"/>
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Reverse flow</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>check-valve failure / pressure reversal (generic)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>possible contamination / backflow to upstream (generic)</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>(none found in extraction — verify)</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1604,58 +1612,58 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>High pressure</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>blocked outlet (generic); upstream pressure source (generic)</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>possible overpressure of section (generic)</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>(none found in extraction — verify)</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr"/>
-      <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr"/>
+      <c r="F4" s="7" t="inlineStr"/>
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Low pressure</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>upstream supply loss (generic); leak / rupture (generic)</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>loss of process function / possible gas breakthrough (generic)</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>(none found in extraction — verify)</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1736,116 +1744,116 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>No flow</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>blocked line / closed valve (generic); pump/compressor stop (generic)</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>loss of process function (generic); functions affected: 13-HS2279, 13-XV2279, 13-XY2279; safety functions in node: 13-HS2279, 13-XV2279, 13-ZL2279, 13-ZS2279</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>13-XV2279</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr"/>
-      <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr"/>
+      <c r="F4" s="7" t="inlineStr"/>
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Low flow</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>partial blockage / fouling (generic)</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>reduced capacity (generic); functions affected: 13-HS2279, 13-XV2279, 13-XY2279; safety functions in node: 13-HS2279, 13-XV2279, 13-ZL2279, 13-ZS2279</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>13-XV2279</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>High flow</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>control valve fully open (generic)</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>possible downstream overload (generic); functions affected: 13-HS2279, 13-XV2279, 13-XY2279; safety functions in node: 13-HS2279, 13-XV2279, 13-ZL2279, 13-ZS2279</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>13-XV2279</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr"/>
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Reverse flow</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>check-valve failure / pressure reversal (generic)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>possible contamination / backflow to upstream (generic); functions affected: 13-HS2279, 13-XV2279, 13-XY2279; safety functions in node: 13-HS2279, 13-XV2279, 13-ZL2279, 13-ZS2279</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>13-XV2279</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1926,58 +1934,58 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>High temperature</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>loss of cooling (generic)</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>possible material/design-limit exceedance (generic)</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>(none found in extraction — verify)</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr"/>
-      <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr"/>
+      <c r="F4" s="7" t="inlineStr"/>
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Low temperature</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>JT-cooling on depressurisation (generic); loss of heating (generic)</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>possible hydrate formation / brittle fracture risk (generic)</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>(none found in extraction — verify)</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2058,116 +2066,116 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>High pressure</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>blocked outlet (generic); upstream pressure source (generic)</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>possible overpressure of section (generic)</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>(none found in extraction — verify)</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr"/>
-      <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr"/>
+      <c r="F4" s="7" t="inlineStr"/>
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Low pressure</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>upstream supply loss (generic); leak / rupture (generic)</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>loss of process function / possible gas breakthrough (generic)</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>(none found in extraction — verify)</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>High temperature</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>loss of cooling (generic)</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>possible material/design-limit exceedance (generic)</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>(none found in extraction — verify)</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr"/>
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Low temperature</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>JT-cooling on depressurisation (generic); loss of heating (generic)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>possible hydrate formation / brittle fracture risk (generic)</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>(none found in extraction — verify)</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2248,116 +2256,116 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>No flow</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>blocked line / closed valve (generic); pump/compressor stop (generic)</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>loss of process function (generic); functions affected: 13-HS2287; safety functions in node: 13-HS2287, 13-ZL2287, 13-ZS2287</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>(none found in extraction — verify)</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr"/>
-      <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr"/>
+      <c r="F4" s="7" t="inlineStr"/>
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Low flow</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>partial blockage / fouling (generic)</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>reduced capacity (generic); functions affected: 13-HS2287; safety functions in node: 13-HS2287, 13-ZL2287, 13-ZS2287</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>(none found in extraction — verify)</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>High flow</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>control valve fully open (generic)</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>possible downstream overload (generic); functions affected: 13-HS2287; safety functions in node: 13-HS2287, 13-ZL2287, 13-ZS2287</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>(none found in extraction — verify)</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr"/>
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Reverse flow</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>check-valve failure / pressure reversal (generic)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>possible contamination / backflow to upstream (generic); functions affected: 13-HS2287; safety functions in node: 13-HS2287, 13-ZL2287, 13-ZS2287</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>(none found in extraction — verify)</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2462,34 +2470,34 @@
       <c r="F4" s="6" t="inlineStr"/>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>reviewed</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Low pressure</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>upstream supply loss (generic); leak / rupture (generic)</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>loss of process function / possible gas breakthrough (generic)</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>(none found in extraction — verify)</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2570,58 +2578,58 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>High pressure</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>blocked outlet (generic); upstream pressure source (generic)</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>possible overpressure of section (generic)</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>(none found in extraction — verify)</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr"/>
-      <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr"/>
+      <c r="F4" s="7" t="inlineStr"/>
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Low pressure</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>upstream supply loss (generic); leak / rupture (generic)</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>loss of process function / possible gas breakthrough (generic)</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>(none found in extraction — verify)</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2702,58 +2710,58 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>High pressure</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>blocked outlet (generic); upstream pressure source (generic)</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>possible overpressure of section (generic)</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>(none found in extraction — verify)</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr"/>
-      <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr"/>
+      <c r="F4" s="7" t="inlineStr"/>
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Low pressure</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>upstream supply loss (generic); leak / rupture (generic)</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>loss of process function / possible gas breakthrough (generic)</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>(none found in extraction — verify)</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2834,58 +2842,58 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>High pressure</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>blocked outlet (generic); upstream pressure source (generic)</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>possible overpressure of section (generic)</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>(none found in extraction — verify)</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr"/>
-      <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr"/>
+      <c r="F4" s="7" t="inlineStr"/>
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Low pressure</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>upstream supply loss (generic); leak / rupture (generic)</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>loss of process function / possible gas breakthrough (generic)</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>(none found in extraction — verify)</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2966,58 +2974,58 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>High pressure</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>blocked outlet (generic); upstream pressure source (generic)</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>possible overpressure of section (generic)</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>(none found in extraction — verify)</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr"/>
-      <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr"/>
+      <c r="F4" s="7" t="inlineStr"/>
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Low pressure</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>upstream supply loss (generic); leak / rupture (generic)</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>loss of process function / possible gas breakthrough (generic)</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>(none found in extraction — verify)</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -3098,58 +3106,58 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>High pressure</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>blocked outlet (generic); upstream pressure source (generic)</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>possible overpressure of section (generic)</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>(none found in extraction — verify)</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr"/>
-      <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr"/>
+      <c r="F4" s="7" t="inlineStr"/>
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Low pressure</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>upstream supply loss (generic); leak / rupture (generic)</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>loss of process function / possible gas breakthrough (generic)</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>(none found in extraction — verify)</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -3230,58 +3238,58 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>High temperature</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>loss of cooling (generic)</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>possible material/design-limit exceedance (generic)</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>(none found in extraction — verify)</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr"/>
-      <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr"/>
+      <c r="F4" s="7" t="inlineStr"/>
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Low temperature</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>JT-cooling on depressurisation (generic); loss of heating (generic)</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>possible hydrate formation / brittle fracture risk (generic)</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>(none found in extraction — verify)</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -3362,58 +3370,58 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>High pressure</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>blocked outlet (generic); upstream pressure source (generic)</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>possible overpressure of section (generic)</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>(none found in extraction — verify)</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr"/>
-      <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr"/>
+      <c r="F4" s="7" t="inlineStr"/>
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Low pressure</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>upstream supply loss (generic); leak / rupture (generic)</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>loss of process function / possible gas breakthrough (generic)</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>(none found in extraction — verify)</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>

--- a/reports/hazop_system_13.xlsx
+++ b/reports/hazop_system_13.xlsx
@@ -487,7 +487,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>HAZOP preparation — System 13</t>
+          <t>HAZOP preparation — System 13 (functional loops)</t>
         </is>
       </c>
     </row>
@@ -978,16 +978,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1027,15 +1030,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1064,7 +1082,10 @@
       </c>
       <c r="E4" s="7" t="inlineStr"/>
       <c r="F4" s="7" t="inlineStr"/>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr"/>
+      <c r="H4" s="7" t="inlineStr"/>
+      <c r="I4" s="7" t="inlineStr"/>
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1093,7 +1114,10 @@
       </c>
       <c r="E5" s="7" t="inlineStr"/>
       <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1122,7 +1146,10 @@
       </c>
       <c r="E6" s="7" t="inlineStr"/>
       <c r="F6" s="7" t="inlineStr"/>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr"/>
+      <c r="H6" s="7" t="inlineStr"/>
+      <c r="I6" s="7" t="inlineStr"/>
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1151,7 +1178,10 @@
       </c>
       <c r="E7" s="7" t="inlineStr"/>
       <c r="F7" s="7" t="inlineStr"/>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr"/>
+      <c r="I7" s="7" t="inlineStr"/>
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1168,16 +1198,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1217,15 +1250,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1254,7 +1302,10 @@
       </c>
       <c r="E4" s="7" t="inlineStr"/>
       <c r="F4" s="7" t="inlineStr"/>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr"/>
+      <c r="H4" s="7" t="inlineStr"/>
+      <c r="I4" s="7" t="inlineStr"/>
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1283,7 +1334,10 @@
       </c>
       <c r="E5" s="7" t="inlineStr"/>
       <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1312,7 +1366,10 @@
       </c>
       <c r="E6" s="7" t="inlineStr"/>
       <c r="F6" s="7" t="inlineStr"/>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr"/>
+      <c r="H6" s="7" t="inlineStr"/>
+      <c r="I6" s="7" t="inlineStr"/>
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1341,7 +1398,10 @@
       </c>
       <c r="E7" s="7" t="inlineStr"/>
       <c r="F7" s="7" t="inlineStr"/>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr"/>
+      <c r="I7" s="7" t="inlineStr"/>
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1358,16 +1418,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1407,15 +1470,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1444,7 +1522,10 @@
       </c>
       <c r="E4" s="7" t="inlineStr"/>
       <c r="F4" s="7" t="inlineStr"/>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr"/>
+      <c r="H4" s="7" t="inlineStr"/>
+      <c r="I4" s="7" t="inlineStr"/>
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1473,7 +1554,10 @@
       </c>
       <c r="E5" s="7" t="inlineStr"/>
       <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1502,7 +1586,10 @@
       </c>
       <c r="E6" s="7" t="inlineStr"/>
       <c r="F6" s="7" t="inlineStr"/>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr"/>
+      <c r="H6" s="7" t="inlineStr"/>
+      <c r="I6" s="7" t="inlineStr"/>
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1531,7 +1618,10 @@
       </c>
       <c r="E7" s="7" t="inlineStr"/>
       <c r="F7" s="7" t="inlineStr"/>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr"/>
+      <c r="I7" s="7" t="inlineStr"/>
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1548,16 +1638,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1597,15 +1690,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1634,7 +1742,10 @@
       </c>
       <c r="E4" s="7" t="inlineStr"/>
       <c r="F4" s="7" t="inlineStr"/>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr"/>
+      <c r="H4" s="7" t="inlineStr"/>
+      <c r="I4" s="7" t="inlineStr"/>
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1663,7 +1774,10 @@
       </c>
       <c r="E5" s="7" t="inlineStr"/>
       <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1680,16 +1794,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1729,15 +1846,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1766,7 +1898,10 @@
       </c>
       <c r="E4" s="7" t="inlineStr"/>
       <c r="F4" s="7" t="inlineStr"/>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr"/>
+      <c r="H4" s="7" t="inlineStr"/>
+      <c r="I4" s="7" t="inlineStr"/>
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1795,7 +1930,10 @@
       </c>
       <c r="E5" s="7" t="inlineStr"/>
       <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1824,7 +1962,10 @@
       </c>
       <c r="E6" s="7" t="inlineStr"/>
       <c r="F6" s="7" t="inlineStr"/>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr"/>
+      <c r="H6" s="7" t="inlineStr"/>
+      <c r="I6" s="7" t="inlineStr"/>
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1853,7 +1994,10 @@
       </c>
       <c r="E7" s="7" t="inlineStr"/>
       <c r="F7" s="7" t="inlineStr"/>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr"/>
+      <c r="I7" s="7" t="inlineStr"/>
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1870,16 +2014,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1919,15 +2066,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1956,7 +2118,10 @@
       </c>
       <c r="E4" s="7" t="inlineStr"/>
       <c r="F4" s="7" t="inlineStr"/>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr"/>
+      <c r="H4" s="7" t="inlineStr"/>
+      <c r="I4" s="7" t="inlineStr"/>
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1985,7 +2150,10 @@
       </c>
       <c r="E5" s="7" t="inlineStr"/>
       <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2002,16 +2170,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2051,15 +2222,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2088,7 +2274,10 @@
       </c>
       <c r="E4" s="7" t="inlineStr"/>
       <c r="F4" s="7" t="inlineStr"/>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr"/>
+      <c r="H4" s="7" t="inlineStr"/>
+      <c r="I4" s="7" t="inlineStr"/>
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2117,7 +2306,10 @@
       </c>
       <c r="E5" s="7" t="inlineStr"/>
       <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2146,7 +2338,10 @@
       </c>
       <c r="E6" s="7" t="inlineStr"/>
       <c r="F6" s="7" t="inlineStr"/>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr"/>
+      <c r="H6" s="7" t="inlineStr"/>
+      <c r="I6" s="7" t="inlineStr"/>
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2175,7 +2370,10 @@
       </c>
       <c r="E7" s="7" t="inlineStr"/>
       <c r="F7" s="7" t="inlineStr"/>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr"/>
+      <c r="I7" s="7" t="inlineStr"/>
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2192,16 +2390,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2241,15 +2442,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2278,7 +2494,10 @@
       </c>
       <c r="E4" s="7" t="inlineStr"/>
       <c r="F4" s="7" t="inlineStr"/>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr"/>
+      <c r="H4" s="7" t="inlineStr"/>
+      <c r="I4" s="7" t="inlineStr"/>
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2307,7 +2526,10 @@
       </c>
       <c r="E5" s="7" t="inlineStr"/>
       <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2336,7 +2558,10 @@
       </c>
       <c r="E6" s="7" t="inlineStr"/>
       <c r="F6" s="7" t="inlineStr"/>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr"/>
+      <c r="H6" s="7" t="inlineStr"/>
+      <c r="I6" s="7" t="inlineStr"/>
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2365,7 +2590,10 @@
       </c>
       <c r="E7" s="7" t="inlineStr"/>
       <c r="F7" s="7" t="inlineStr"/>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr"/>
+      <c r="I7" s="7" t="inlineStr"/>
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2382,16 +2610,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2431,15 +2662,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2468,7 +2714,10 @@
       </c>
       <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
@@ -2497,7 +2746,10 @@
       </c>
       <c r="E5" s="7" t="inlineStr"/>
       <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2514,16 +2766,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2563,15 +2818,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2600,7 +2870,10 @@
       </c>
       <c r="E4" s="7" t="inlineStr"/>
       <c r="F4" s="7" t="inlineStr"/>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr"/>
+      <c r="H4" s="7" t="inlineStr"/>
+      <c r="I4" s="7" t="inlineStr"/>
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2629,7 +2902,10 @@
       </c>
       <c r="E5" s="7" t="inlineStr"/>
       <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2646,16 +2922,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2695,15 +2974,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2732,7 +3026,10 @@
       </c>
       <c r="E4" s="7" t="inlineStr"/>
       <c r="F4" s="7" t="inlineStr"/>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr"/>
+      <c r="H4" s="7" t="inlineStr"/>
+      <c r="I4" s="7" t="inlineStr"/>
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2761,7 +3058,10 @@
       </c>
       <c r="E5" s="7" t="inlineStr"/>
       <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2778,16 +3078,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2827,15 +3130,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2864,7 +3182,10 @@
       </c>
       <c r="E4" s="7" t="inlineStr"/>
       <c r="F4" s="7" t="inlineStr"/>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr"/>
+      <c r="H4" s="7" t="inlineStr"/>
+      <c r="I4" s="7" t="inlineStr"/>
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2893,7 +3214,10 @@
       </c>
       <c r="E5" s="7" t="inlineStr"/>
       <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -2910,16 +3234,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2959,15 +3286,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2996,7 +3338,10 @@
       </c>
       <c r="E4" s="7" t="inlineStr"/>
       <c r="F4" s="7" t="inlineStr"/>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr"/>
+      <c r="H4" s="7" t="inlineStr"/>
+      <c r="I4" s="7" t="inlineStr"/>
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -3025,7 +3370,10 @@
       </c>
       <c r="E5" s="7" t="inlineStr"/>
       <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -3042,16 +3390,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3091,15 +3442,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -3128,7 +3494,10 @@
       </c>
       <c r="E4" s="7" t="inlineStr"/>
       <c r="F4" s="7" t="inlineStr"/>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr"/>
+      <c r="H4" s="7" t="inlineStr"/>
+      <c r="I4" s="7" t="inlineStr"/>
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -3157,7 +3526,10 @@
       </c>
       <c r="E5" s="7" t="inlineStr"/>
       <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -3174,16 +3546,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3223,15 +3598,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -3260,7 +3650,10 @@
       </c>
       <c r="E4" s="7" t="inlineStr"/>
       <c r="F4" s="7" t="inlineStr"/>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr"/>
+      <c r="H4" s="7" t="inlineStr"/>
+      <c r="I4" s="7" t="inlineStr"/>
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -3289,7 +3682,10 @@
       </c>
       <c r="E5" s="7" t="inlineStr"/>
       <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -3306,16 +3702,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3355,15 +3754,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -3392,7 +3806,10 @@
       </c>
       <c r="E4" s="7" t="inlineStr"/>
       <c r="F4" s="7" t="inlineStr"/>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr"/>
+      <c r="H4" s="7" t="inlineStr"/>
+      <c r="I4" s="7" t="inlineStr"/>
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -3421,7 +3838,10 @@
       </c>
       <c r="E5" s="7" t="inlineStr"/>
       <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
